--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486307_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486307_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5606</v>
+        <v>4.8776</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2611</v>
+        <v>4.5473</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2995</v>
+        <v>0.3304</v>
       </c>
       <c r="G2" t="n">
         <v>4.516</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5671</v>
+        <v>0.8841</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1342</v>
+        <v>1.4204</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5671</v>
+        <v>-0.5363</v>
       </c>
       <c r="V2" t="n">
         <v>0.5649999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4412</v>
+        <v>4.825</v>
       </c>
       <c r="E3" t="n">
-        <v>3.844</v>
+        <v>5.012</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4028</v>
+        <v>-0.187</v>
       </c>
       <c r="G3" t="n">
         <v>2.2637</v>
@@ -688,13 +688,13 @@
         <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.9747</v>
+        <v>-0.5909</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5924</v>
+        <v>0.5756</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.3823</v>
+        <v>-1.1666</v>
       </c>
       <c r="V3" t="n">
         <v>2.0647</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. IGLESIAS FERNANDEZ</t>
+          <t>K. SMITH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0361</v>
+        <v>1.2965</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4047</v>
+        <v>-0.7738</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3686</v>
+        <v>2.0704</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2562</v>
+        <v>1.173</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.465</v>
+        <v>-1.0399</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7211</v>
+        <v>2.2129</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2331</v>
+        <v>1.7142</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.845</v>
+        <v>-0.772</v>
       </c>
       <c r="L4" t="n">
-        <v>0.612</v>
+        <v>2.4862</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4892</v>
+        <v>-0.5412</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3801</v>
+        <v>-0.2679</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1091</v>
+        <v>-0.2733</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6525</v>
+        <v>2.6101</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2574</v>
+        <v>0.6456</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6377</v>
+        <v>0.6441</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3803</v>
+        <v>0.0015</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.13</v>
+        <v>-0.7395</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. SMITH</t>
+          <t>M. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5689</v>
+        <v>0.9176</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5323</v>
+        <v>1.1321</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1012</v>
+        <v>-0.2145</v>
       </c>
       <c r="G5" t="n">
-        <v>1.173</v>
+        <v>0.2562</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0399</v>
+        <v>-0.465</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2129</v>
+        <v>0.7211</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7142</v>
+        <v>-0.2331</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.772</v>
+        <v>-0.845</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4862</v>
+        <v>0.612</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5412</v>
+        <v>0.4892</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2679</v>
+        <v>0.3801</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2733</v>
+        <v>0.1091</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.6101</v>
+        <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>0.918</v>
+        <v>1.1389</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8857</v>
+        <v>1.3651</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0323</v>
+        <v>-0.2262</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7395</v>
+        <v>-1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4718</v>
+        <v>0.8871</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1874</v>
+        <v>0.4794</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2844</v>
+        <v>0.4077</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2496</v>
@@ -922,13 +922,13 @@
         <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8512999999999999</v>
+        <v>1.2666</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8496</v>
+        <v>1.1416</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0017</v>
+        <v>0.125</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>D. SARAIVA SEIXAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4092</v>
+        <v>0.2004</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9496</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5405</v>
+        <v>0.2004</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2492</v>
+        <v>0.149</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1612</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4104</v>
+        <v>0.149</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1016</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0251</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0765</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3508</v>
+        <v>0.149</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8639</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4869</v>
+        <v>0.149</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2451</v>
+        <v>0.0514</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8496</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3955</v>
+        <v>0.0514</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.6743</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2159</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.8902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. SARAIVA SEIXAS</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1696</v>
+        <v>0.0452</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1.8631</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1696</v>
+        <v>-1.8179</v>
       </c>
       <c r="G8" t="n">
-        <v>0.149</v>
+        <v>-0.2492</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.1612</v>
       </c>
       <c r="I8" t="n">
-        <v>0.149</v>
+        <v>-0.4104</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.1016</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.0251</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.0765</v>
       </c>
       <c r="M8" t="n">
-        <v>0.149</v>
+        <v>-1.3508</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.8639</v>
       </c>
       <c r="O8" t="n">
-        <v>0.149</v>
+        <v>-0.4869</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0205</v>
+        <v>0.8811</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.7631</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0205</v>
+        <v>0.1181</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.6743</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2159</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9274</v>
+        <v>-0.5368000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.608</v>
+        <v>-1.1009</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3194</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0776</v>
+        <v>0.3392</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.289</v>
+        <v>-1.3262</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3665</v>
+        <v>1.6654</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0649</v>
+        <v>0.2048</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0881</v>
+        <v>-0.9244</v>
       </c>
       <c r="L9" t="n">
-        <v>0.153</v>
+        <v>1.1292</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0127</v>
+        <v>0.1345</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2009</v>
+        <v>-0.4018</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2136</v>
+        <v>0.5362</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2175</v>
+        <v>-0.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="R9" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3425</v>
+        <v>-0.2013</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4146</v>
+        <v>0.8917</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0721</v>
+        <v>-1.093</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. JÜRGENS</t>
+          <t>I. VAZQUEZ PEREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.345</v>
+        <v>-0.9355</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5974</v>
+        <v>0.4359</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9423</v>
+        <v>-1.3715</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6376</v>
+        <v>1.6812</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5675</v>
+        <v>2.1442</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.463</v>
       </c>
       <c r="J10" t="n">
-        <v>2.3643</v>
+        <v>3.1349</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9564</v>
+        <v>3.3245</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5921</v>
+        <v>-0.1896</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2732</v>
+        <v>-1.4537</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6111</v>
+        <v>-1.1803</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3379</v>
+        <v>-0.2733</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.9576</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1697</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1476</v>
+        <v>0.5636</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0221</v>
+        <v>-0.4849</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.1947</v>
+        <v>-0.9554</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4552</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5877</v>
+        <v>-1.2341</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9664</v>
+        <v>-0.6744</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6213</v>
+        <v>-0.5596</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9921</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0959</v>
+        <v>0.2578</v>
       </c>
       <c r="T11" t="n">
-        <v>0.161</v>
+        <v>0.453</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2569</v>
+        <v>-0.1953</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3698</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ PEREZ</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7269</v>
+        <v>-1.3907</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6636</v>
+        <v>-0.763</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0632</v>
+        <v>-0.6276</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6812</v>
+        <v>0.0776</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1442</v>
+        <v>-0.289</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.463</v>
+        <v>0.3665</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1349</v>
+        <v>0.0649</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3245</v>
+        <v>-0.0881</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1896</v>
+        <v>0.153</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4537</v>
+        <v>0.0127</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1803</v>
+        <v>-0.2009</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2733</v>
+        <v>0.2136</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.7401</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7126</v>
+        <v>-0.1208</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.536</v>
+        <v>0.2596</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1767</v>
+        <v>-0.3803</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9554</v>
+        <v>-1.13</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.9554</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>C. JÜRGENS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.9764</v>
+        <v>-1.4884</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3555</v>
+        <v>0.3306</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3791</v>
+        <v>-1.819</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3392</v>
+        <v>2.6376</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.3262</v>
+        <v>3.5675</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6654</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2048</v>
+        <v>2.3643</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.9244</v>
+        <v>2.9564</v>
       </c>
       <c r="L13" t="n">
-        <v>1.1292</v>
+        <v>-0.5921</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1345</v>
+        <v>0.2732</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4018</v>
+        <v>0.6111</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5362</v>
+        <v>-0.3379</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.87</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.3926</v>
+        <v>-2.1751</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6408</v>
+        <v>1.0262</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3629</v>
+        <v>0.8808</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2779</v>
+        <v>0.1454</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1952</v>
+        <v>-3.1947</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1952</v>
+        <v>-0.7395</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.093999999999999</v>
+        <v>7.463900000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>9.118400000000001</v>
+        <v>10.4883</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.024299999999999</v>
+        <v>-3.0242</v>
       </c>
       <c r="G14" t="n">
         <v>9.602600000000001</v>
@@ -1525,16 +1525,16 @@
         <v>7.910599999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>5.936700000000001</v>
+        <v>5.9367</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.244599999999999</v>
+        <v>-4.2446</v>
       </c>
       <c r="N14" t="n">
         <v>-3.4238</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8209999999999997</v>
+        <v>-0.821</v>
       </c>
       <c r="P14" t="n">
         <v>-1.0877</v>
@@ -1546,22 +1546,22 @@
         <v>14.1377</v>
       </c>
       <c r="S14" t="n">
-        <v>3.947599999999999</v>
+        <v>5.3174</v>
       </c>
       <c r="T14" t="n">
-        <v>7.588700000000001</v>
+        <v>8.958600000000002</v>
       </c>
       <c r="U14" t="n">
         <v>-3.6412</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.368799999999999</v>
+        <v>-6.3688</v>
       </c>
       <c r="W14" t="n">
         <v>2.9077</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.276399999999999</v>
+        <v>-9.276400000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9147</v>
+        <v>5.2981</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0211</v>
+        <v>6.8034</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1064</v>
+        <v>-1.5052</v>
       </c>
       <c r="G15" t="n">
         <v>0.2186</v>
@@ -1624,13 +1624,13 @@
         <v>2.6101</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0413</v>
+        <v>0.3422</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0277</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0689</v>
+        <v>-0.4678</v>
       </c>
       <c r="V15" t="n">
         <v>4.5199</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9348</v>
+        <v>4.0626</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8835</v>
+        <v>3.107</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0513</v>
+        <v>0.9556</v>
       </c>
       <c r="G16" t="n">
         <v>3.5553</v>
@@ -1702,13 +1702,13 @@
         <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.9696</v>
+        <v>-0.8418</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6044</v>
+        <v>-0.3809</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.3651</v>
+        <v>-0.4609</v>
       </c>
       <c r="V16" t="n">
         <v>0.9141</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9394</v>
+        <v>0.22</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5368</v>
+        <v>0.6427</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5974</v>
+        <v>-0.4227</v>
       </c>
       <c r="G17" t="n">
         <v>-3.0682</v>
@@ -1780,13 +1780,13 @@
         <v>2.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2469</v>
+        <v>0.5275</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1823</v>
+        <v>1.2882</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9354</v>
+        <v>-0.7607</v>
       </c>
       <c r="V17" t="n">
         <v>0.5857</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. ARTEAGA GONZALEZ</t>
+          <t>N. GALETTE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7115</v>
+        <v>-0.0728</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4638</v>
+        <v>-1.1598</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7523</v>
+        <v>1.087</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2168</v>
+        <v>-0.9947</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0613</v>
+        <v>-1.174</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2782</v>
+        <v>0.1793</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8814</v>
+        <v>-1.3389</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8432</v>
+        <v>-1.4536</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0382</v>
+        <v>0.1147</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0983</v>
+        <v>0.3442</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7819</v>
+        <v>0.2796</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3164</v>
+        <v>0.0645</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.1751</v>
+        <v>0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1034</v>
+        <v>-0.2749</v>
       </c>
       <c r="T18" t="n">
-        <v>2.6498</v>
+        <v>0.1791</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4536</v>
+        <v>-0.4539</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5443</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1952</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. GALETTE</t>
+          <t>P. FIGUERAS LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2655</v>
+        <v>-0.1373</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9363</v>
+        <v>-0.0252</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6708</v>
+        <v>-0.1121</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9947</v>
+        <v>-0.0335</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.174</v>
+        <v>-0.0335</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1793</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3389</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4536</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1147</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3442</v>
+        <v>-0.0335</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2796</v>
+        <v>-0.0335</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0645</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4676</v>
+        <v>0.0261</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4026</v>
+        <v>-0.0252</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8702</v>
+        <v>0.0514</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5443</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.5443</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. FIGUERAS LOPEZ</t>
+          <t>J. CONE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2799</v>
+        <v>-0.1722</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.137</v>
+        <v>0.8398</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1429</v>
+        <v>-1.012</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0335</v>
+        <v>-1.0364</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0335</v>
+        <v>-2.0684</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1.032</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.6158</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-1.0521</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.6679</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0335</v>
+        <v>-1.6521</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0335</v>
+        <v>-1.0162</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.6359</v>
       </c>
       <c r="P20" t="n">
-        <v>0.435</v>
+        <v>-0.435</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
-        <v>0.435</v>
+        <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1164</v>
+        <v>-0.9608</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.137</v>
+        <v>0.3137</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0205</v>
+        <v>-1.2744</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5649999999999999</v>
+        <v>2.2599</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.0854</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. SCHOTT</t>
+          <t>V. ARTEAGA GONZALEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0938</v>
+        <v>-1.2037</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1774</v>
+        <v>0.011</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9164</v>
+        <v>-1.2147</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1743</v>
+        <v>-0.2168</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6213</v>
+        <v>1.0613</v>
       </c>
       <c r="I21" t="n">
-        <v>0.447</v>
+        <v>-1.2782</v>
       </c>
       <c r="J21" t="n">
-        <v>0.838</v>
+        <v>1.8814</v>
       </c>
       <c r="K21" t="n">
-        <v>0.073</v>
+        <v>1.8432</v>
       </c>
       <c r="L21" t="n">
-        <v>0.765</v>
+        <v>0.0382</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0123</v>
+        <v>-2.0983</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6943</v>
+        <v>-0.7819</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.318</v>
+        <v>-1.3164</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.305</v>
+        <v>-3.2626</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2534</v>
+        <v>1.1882</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2896</v>
+        <v>1.1969</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0362</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3904</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CONE</t>
+          <t>F. SCHOTT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4002</v>
+        <v>-1.5074</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0543</v>
+        <v>-0.401</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3459</v>
+        <v>-1.1064</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0364</v>
+        <v>-1.1743</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0684</v>
+        <v>-1.6213</v>
       </c>
       <c r="I22" t="n">
-        <v>1.032</v>
+        <v>0.447</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6158</v>
+        <v>0.838</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0521</v>
+        <v>0.073</v>
       </c>
       <c r="L22" t="n">
-        <v>1.6679</v>
+        <v>0.765</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6521</v>
+        <v>-2.0123</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0162</v>
+        <v>-1.6943</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6359</v>
+        <v>-0.318</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1751</v>
+        <v>-1.305</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.1888</v>
+        <v>-0.1601</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5804</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.6084</v>
+        <v>-0.2262</v>
       </c>
       <c r="V22" t="n">
-        <v>2.2599</v>
+        <v>-0.3904</v>
       </c>
       <c r="W22" t="n">
-        <v>2.0854</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.1745</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. MOLINS CALDERON</t>
+          <t>E. WEMBI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2483</v>
+        <v>-4.7935</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4509</v>
+        <v>-4.4544</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7974</v>
+        <v>-0.3391</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3988</v>
+        <v>-4.4537</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.837</v>
+        <v>-1.758</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5618</v>
+        <v>-2.6958</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8034</v>
+        <v>-2.6812</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7086</v>
+        <v>-0.7903</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0948</v>
+        <v>-1.8909</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5954</v>
+        <v>-1.7725</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1284</v>
+        <v>-0.9677</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.467</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.305</v>
+        <v>-2.3926</v>
       </c>
       <c r="R23" t="n">
-        <v>0.435</v>
+        <v>2.8276</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8495</v>
+        <v>-0.405</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3425</v>
+        <v>0.4242</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.507</v>
+        <v>-0.8292</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.13</v>
+        <v>-0.3698</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. WEMBI</t>
+          <t>P. MOLINS CALDERON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.3066</v>
+        <v>-4.8077</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.1249</v>
+        <v>-2.3391</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1817</v>
+        <v>-2.4685</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.4537</v>
+        <v>-2.3988</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.758</v>
+        <v>-1.837</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.6958</v>
+        <v>-0.5618</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.6812</v>
+        <v>-0.8034</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7903</v>
+        <v>-0.7086</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.8909</v>
+        <v>-0.0948</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.7725</v>
+        <v>-1.5954</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9677</v>
+        <v>-1.1284</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.467</v>
       </c>
       <c r="P24" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.305</v>
+      </c>
+      <c r="R24" t="n">
         <v>0.435</v>
       </c>
-      <c r="Q24" t="n">
-        <v>-2.3926</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2.8276</v>
-      </c>
       <c r="S24" t="n">
-        <v>-1.9181</v>
+        <v>-0.4089</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2463</v>
+        <v>-0.2307</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.6718</v>
+        <v>-0.1782</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3698</v>
+        <v>-1.13</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.093900000000001</v>
+        <v>-3.1139</v>
       </c>
       <c r="E25" t="n">
         <v>3.0244</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.1183</v>
+        <v>-6.1381</v>
       </c>
       <c r="G25" t="n">
         <v>-9.602500000000001</v>
@@ -2383,7 +2383,7 @@
         <v>3.4236</v>
       </c>
       <c r="L25" t="n">
-        <v>0.821</v>
+        <v>0.8210000000000002</v>
       </c>
       <c r="M25" t="n">
         <v>-13.8473</v>
@@ -2404,13 +2404,13 @@
         <v>15.2255</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.9476</v>
+        <v>-0.9675</v>
       </c>
       <c r="T25" t="n">
         <v>3.6414</v>
       </c>
       <c r="U25" t="n">
-        <v>-7.5889</v>
+        <v>-4.6086</v>
       </c>
       <c r="V25" t="n">
         <v>6.3687</v>
